--- a/outputs/reports/stacked_ensemble_v2/feature_importance_top10.xlsx
+++ b/outputs/reports/stacked_ensemble_v2/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1523185775533347</v>
+        <v>0.1720786854411036</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01038651242041072</v>
+        <v>0.0481293347089442</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=15.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1017649070201782</v>
+        <v>0.09087489223856447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006939287956237106</v>
+        <v>0.02541714038538539</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=10.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.09821405086930558</v>
+        <v>0.08293320097181266</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006697157205631743</v>
+        <v>0.02319589888674889</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.82%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.29%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09397932612641352</v>
+        <v>0.05972465320410667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006408393866020934</v>
+        <v>0.01670461287560165</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=9.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=5.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.06452037139325294</v>
+        <v>0.05431698842707499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004399605416554542</v>
+        <v>0.01519212277620113</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=6.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=5.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06323154212367597</v>
+        <v>0.05205987617231388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004311720921890305</v>
+        <v>0.01456082256079916</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=6.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>법인사업자누적집행건수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04121623398826991</v>
+        <v>0.04831892160192288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002810510268137334</v>
+        <v>0.01351450090749406</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 법인사업자누적집행건수(CORP_BZR_CUMU_EXE_CNT). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>회계연도</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03855966753465484</v>
+        <v>0.04407116173358786</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00262936059546226</v>
+        <v>0.01232642897434177</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.86%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0350877192982458</v>
+        <v>0.04359570521695944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002392610528203665</v>
+        <v>0.01219344675304168</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>인건비집행평균금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02843315184513099</v>
+        <v>0.03278037566289588</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001938839565958195</v>
+        <v>0.009168466554240584</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비집행평균금액(LBST_EXE_AVG_AMT). 기여도(정규화 비중)=3.28%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
